--- a/DownloadedExcels/section_bulk_file.xlsx
+++ b/DownloadedExcels/section_bulk_file.xlsx
@@ -65,7 +65,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -86,93 +86,173 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Section Local Name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Outlet Code</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Outlet Name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>50250327</t>
+          <t>15437620</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PHSEC0011111</t>
+          <t>SEC000SFeb23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PHSEC001</t>
+          <t>Pureit Careline</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1000000003</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aautomation_Outlet_03</t>
+          <t>C0000023668</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Liaqat Store</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2027-10-07</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2027-10-07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>50250327</t>
+          <t>15437620</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PHSEC0011111</t>
+          <t>SEC000SFeb23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PHSEC001</t>
+          <t>Pureit Careline</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1000000004</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aautomation_Outlet_04</t>
+          <t>C0000029627</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>C0000029600</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2027-10-08</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2027-10-08</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>50250327</t>
+          <t>15437620</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PHSEC0011111</t>
+          <t>SEC000SFeb23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PHSEC001</t>
+          <t>Pureit Careline</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1000000005</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aautomation_Outlet_05</t>
+          <t>C0000029637</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>C00000295929</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2027-10-09</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2027-10-09</t>
         </is>
       </c>
     </row>
